--- a/docs/Tableau_Synthese_E5.xlsx
+++ b/docs/Tableau_Synthese_E5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\narmi\Desktop\portfolio1\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1597493-B89A-4D4B-BF2F-C25258DBBC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19C42CF-B0EC-42E1-B4B7-124AB129E73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="810" yWindow="420" windowWidth="20025" windowHeight="13118" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
   <si>
     <t>BTS SERVICES INFORMATIQUES AUX ORGANISATIONS</t>
   </si>
@@ -44,12 +44,6 @@
   </si>
   <si>
     <t>▢ SISR</t>
-  </si>
-  <si>
-    <t>▢ SLAM</t>
-  </si>
-  <si>
-    <t>Adresse URL du portfolio :</t>
   </si>
   <si>
     <t>Compétences mises en œuvre
@@ -122,28 +116,10 @@
     <t>10/24</t>
   </si>
   <si>
-    <t>Configuration d’équipements d’interconnexion réseau (routeurs inter-vlan…)</t>
-  </si>
-  <si>
-    <t>12/24</t>
-  </si>
-  <si>
     <t>Conception et développement site web vitrine SAM Alya (HTML, CSS)</t>
   </si>
   <si>
     <t>11/24</t>
-  </si>
-  <si>
-    <t>GLPI : Prise en main : utilisation et paramétrage (inventaire et ticketing)</t>
-  </si>
-  <si>
-    <t>02-10/24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Développement pages Web en JavaScript </t>
-  </si>
-  <si>
-    <t>Conception et développement site web dynamique GSB Gestion des frais (PHP)</t>
   </si>
   <si>
     <t>05/25</t>
@@ -152,28 +128,10 @@
     <t>Certification l'atelier RGPD: MOOC</t>
   </si>
   <si>
-    <t>Mission 1 : Projet « gestion des adhérents » M2L (Java)</t>
-  </si>
-  <si>
-    <t>09/25</t>
-  </si>
-  <si>
-    <t>GLPI Mise en œuvre d’un serveur LAMP  - Procédure d'installation (ProxMox)</t>
-  </si>
-  <si>
-    <t>11/25</t>
-  </si>
-  <si>
     <t>Mission 2 : Gestion des Formations du CROSL (PHP)</t>
   </si>
   <si>
     <t>12/25</t>
-  </si>
-  <si>
-    <t>Mission 3 : Mobile Forma (Java Android)</t>
-  </si>
-  <si>
-    <t>03/26</t>
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de première année</t>
@@ -186,12 +144,6 @@
   </si>
   <si>
     <t>Refonte ergonomique de l'intranet RH (WordPress &amp; HTML/CSS)</t>
-  </si>
-  <si>
-    <t>Support technique et recueil des besoins utilisateurs</t>
-  </si>
-  <si>
-    <t>Modélisation fonctionnelle (Organigramme de la DRH)</t>
   </si>
   <si>
     <t>Réalisations en milieu professionnel en cours de seconde année</t>
@@ -209,20 +161,29 @@
     <t>02/26</t>
   </si>
   <si>
-    <t>Automatisation du lancement (Systemd) et Scripting Bash</t>
+    <t>Conception graphique des Layouts et gestion des campagnes</t>
   </si>
   <si>
-    <t>Conception graphique des Layouts et gestion des campagnes</t>
+    <t>Adresse URL du portfolio : https://narminf.github.io/Portfolio/</t>
+  </si>
+  <si>
+    <t>Dispositif de veille technologique</t>
+  </si>
+  <si>
+    <t>X SLAM</t>
+  </si>
+  <si>
+    <t>Mission 3 : Mobile Forma (Kotlin Android)</t>
+  </si>
+  <si>
+    <t>GLPI Mise en œuvre d’un serveur LAMP  - Procédure d'installation (ProxMox)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/yyyy"/>
-  </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -284,6 +245,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -653,7 +621,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -662,9 +630,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -697,9 +662,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -718,6 +680,44 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="8" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -729,33 +729,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -974,7 +947,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z998"/>
+  <dimension ref="A1:Z991"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="70.3984375" customWidth="1"/>
@@ -985,124 +958,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="31" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="32" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="33"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="2" spans="1:26" ht="40.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
     </row>
     <row r="3" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+      <c r="A3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
       <c r="E3" s="35"/>
       <c r="F3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="27"/>
-      <c r="H3" s="28"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="37"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="38"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27"/>
       <c r="F4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="30"/>
+    </row>
+    <row r="6" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="38" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="39" t="s">
+      <c r="B6" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="40"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="40"/>
-      <c r="H5" s="41"/>
-    </row>
-    <row r="6" spans="1:26" ht="90" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="22" t="s">
+      <c r="C6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="D6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G6" s="5" t="s">
+    </row>
+    <row r="7" spans="1:26" ht="324.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="39"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" ht="324.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="23"/>
-      <c r="B7" s="25"/>
-      <c r="C7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="F7" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="G7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="H7" s="7" t="s">
         <v>21</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>23</v>
       </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -1124,16 +1097,16 @@
       <c r="Z7" s="1"/>
     </row>
     <row r="8" spans="1:26" ht="48" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="26" t="s">
-        <v>24</v>
+      <c r="A8" s="42" t="s">
+        <v>22</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="37"/>
       <c r="I8" s="1"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
@@ -1154,17 +1127,17 @@
       <c r="Z8" s="1"/>
     </row>
     <row r="9" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="9" t="s">
-        <v>25</v>
+      <c r="A9" s="8" t="s">
+        <v>23</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>26</v>
+      <c r="B9" s="9" t="s">
+        <v>24</v>
       </c>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="12"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="11"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="11"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
@@ -1185,18 +1158,18 @@
       <c r="Z9" s="1"/>
     </row>
     <row r="10" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="9" t="s">
-        <v>27</v>
+      <c r="A10" s="8" t="s">
+        <v>25</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>28</v>
+      <c r="B10" s="9" t="s">
+        <v>26</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="14"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="12"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1217,18 +1190,18 @@
       <c r="Z10" s="1"/>
     </row>
     <row r="11" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
-        <v>29</v>
+      <c r="A11" s="8" t="s">
+        <v>28</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>30</v>
+      <c r="B11" s="9" t="s">
+        <v>27</v>
       </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="12"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="11"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1249,18 +1222,18 @@
       <c r="Z11" s="1"/>
     </row>
     <row r="12" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="9" t="s">
-        <v>31</v>
+      <c r="A12" s="8" t="s">
+        <v>45</v>
       </c>
-      <c r="B12" s="10" t="s">
-        <v>32</v>
+      <c r="B12" s="21">
+        <v>45962</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1281,18 +1254,18 @@
       <c r="Z12" s="1"/>
     </row>
     <row r="13" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="9" t="s">
-        <v>33</v>
+      <c r="A13" s="8" t="s">
+        <v>29</v>
       </c>
-      <c r="B13" s="15">
-        <v>45658</v>
+      <c r="B13" s="9" t="s">
+        <v>30</v>
       </c>
-      <c r="C13" s="11"/>
+      <c r="C13" s="10"/>
       <c r="D13" s="11"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="12"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -1313,18 +1286,18 @@
       <c r="Z13" s="1"/>
     </row>
     <row r="14" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="9" t="s">
-        <v>34</v>
+      <c r="A14" s="8" t="s">
+        <v>44</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>35</v>
+      <c r="B14" s="21">
+        <v>46113</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="11"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
       <c r="I14" s="1"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
@@ -1345,18 +1318,16 @@
       <c r="Z14" s="1"/>
     </row>
     <row r="15" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="9" t="s">
-        <v>36</v>
+      <c r="A15" s="8" t="s">
+        <v>42</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="12"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="11"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
@@ -1377,18 +1348,16 @@
       <c r="Z15" s="1"/>
     </row>
     <row r="16" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>37</v>
+      <c r="A16" s="22" t="s">
+        <v>31</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="11"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="23"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="24"/>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1408,19 +1377,15 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
+    <row r="17" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="14"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="13"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
@@ -1441,16 +1406,16 @@
       <c r="Z17" s="1"/>
     </row>
     <row r="18" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
-        <v>41</v>
+      <c r="A18" s="8" t="s">
+        <v>32</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>42</v>
+      <c r="B18" s="9" t="s">
+        <v>33</v>
       </c>
       <c r="C18" s="11"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="13"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11"/>
       <c r="I18" s="1"/>
@@ -1473,18 +1438,18 @@
       <c r="Z18" s="1"/>
     </row>
     <row r="19" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
-        <v>43</v>
+      <c r="A19" s="8" t="s">
+        <v>34</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>44</v>
+      <c r="B19" s="9" t="s">
+        <v>33</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="12"/>
       <c r="E19" s="12"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
@@ -1505,16 +1470,16 @@
       <c r="Z19" s="1"/>
     </row>
     <row r="20" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="29" t="s">
-        <v>45</v>
+      <c r="A20" s="22" t="s">
+        <v>35</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="31"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="24"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
@@ -1535,14 +1500,14 @@
       <c r="Z20" s="1"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="16"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="14"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="13"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
@@ -1563,18 +1528,18 @@
       <c r="Z21" s="1"/>
     </row>
     <row r="22" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="9" t="s">
-        <v>46</v>
+      <c r="A22" s="8" t="s">
+        <v>36</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>47</v>
+      <c r="B22" s="17" t="s">
+        <v>37</v>
       </c>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
+      <c r="H22" s="11"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
@@ -1595,18 +1560,18 @@
       <c r="Z22" s="1"/>
     </row>
     <row r="23" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="9" t="s">
-        <v>48</v>
+      <c r="A23" s="18" t="s">
+        <v>38</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>47</v>
+      <c r="B23" s="17" t="s">
+        <v>39</v>
       </c>
-      <c r="C23" s="18"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
@@ -1627,18 +1592,18 @@
       <c r="Z23" s="1"/>
     </row>
     <row r="24" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="9" t="s">
-        <v>49</v>
+      <c r="A24" s="19" t="s">
+        <v>40</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>47</v>
+      <c r="B24" s="17" t="s">
+        <v>39</v>
       </c>
-      <c r="C24" s="11"/>
-      <c r="D24" s="12"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
       <c r="E24" s="11"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="14"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="13"/>
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -1659,224 +1624,76 @@
       <c r="Z24" s="1"/>
     </row>
     <row r="25" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
-    </row>
-    <row r="26" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="29" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1"/>
-      <c r="Z26" s="1"/>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+    </row>
+    <row r="26" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="16"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-      <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
-      <c r="V27" s="1"/>
-      <c r="W27" s="1"/>
-      <c r="X27" s="1"/>
-      <c r="Y27" s="1"/>
-      <c r="Z27" s="1"/>
-    </row>
-    <row r="28" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-      <c r="S28" s="1"/>
-      <c r="T28" s="1"/>
-      <c r="U28" s="1"/>
-      <c r="V28" s="1"/>
-      <c r="W28" s="1"/>
-      <c r="X28" s="1"/>
-      <c r="Y28" s="1"/>
-      <c r="Z28" s="1"/>
-    </row>
-    <row r="29" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="20" t="s">
-        <v>54</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-      <c r="S29" s="1"/>
-      <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1"/>
-      <c r="Z29" s="1"/>
-    </row>
-    <row r="30" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-    </row>
-    <row r="31" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C31" s="11"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
-      <c r="U31" s="1"/>
-      <c r="V31" s="1"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-    </row>
-    <row r="32" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+    </row>
+    <row r="28" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+    </row>
+    <row r="29" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+    </row>
+    <row r="31" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+    </row>
+    <row r="32" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -11476,78 +11293,10 @@
       <c r="G991" s="1"/>
       <c r="H991" s="1"/>
     </row>
-    <row r="992" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A992" s="1"/>
-      <c r="B992" s="1"/>
-      <c r="C992" s="1"/>
-      <c r="D992" s="1"/>
-      <c r="E992" s="1"/>
-      <c r="F992" s="1"/>
-      <c r="G992" s="1"/>
-      <c r="H992" s="1"/>
-    </row>
-    <row r="993" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A993" s="1"/>
-      <c r="B993" s="1"/>
-      <c r="C993" s="1"/>
-      <c r="D993" s="1"/>
-      <c r="E993" s="1"/>
-      <c r="F993" s="1"/>
-      <c r="G993" s="1"/>
-      <c r="H993" s="1"/>
-    </row>
-    <row r="994" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A994" s="1"/>
-      <c r="B994" s="1"/>
-      <c r="C994" s="1"/>
-      <c r="D994" s="1"/>
-      <c r="E994" s="1"/>
-      <c r="F994" s="1"/>
-      <c r="G994" s="1"/>
-      <c r="H994" s="1"/>
-    </row>
-    <row r="995" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A995" s="1"/>
-      <c r="B995" s="1"/>
-      <c r="C995" s="1"/>
-      <c r="D995" s="1"/>
-      <c r="E995" s="1"/>
-      <c r="F995" s="1"/>
-      <c r="G995" s="1"/>
-      <c r="H995" s="1"/>
-    </row>
-    <row r="996" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A996" s="1"/>
-      <c r="B996" s="1"/>
-      <c r="C996" s="1"/>
-      <c r="D996" s="1"/>
-      <c r="E996" s="1"/>
-      <c r="F996" s="1"/>
-      <c r="G996" s="1"/>
-      <c r="H996" s="1"/>
-    </row>
-    <row r="997" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A997" s="1"/>
-      <c r="B997" s="1"/>
-      <c r="C997" s="1"/>
-      <c r="D997" s="1"/>
-      <c r="E997" s="1"/>
-      <c r="F997" s="1"/>
-      <c r="G997" s="1"/>
-      <c r="H997" s="1"/>
-    </row>
-    <row r="998" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A998" s="1"/>
-      <c r="B998" s="1"/>
-      <c r="C998" s="1"/>
-      <c r="D998" s="1"/>
-      <c r="E998" s="1"/>
-      <c r="F998" s="1"/>
-      <c r="G998" s="1"/>
-      <c r="H998" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A1:F1"/>
@@ -11558,8 +11307,6 @@
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A26:H26"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.196527777777778" right="0.196527777777778" top="0.196527777777778" bottom="0.196527777777778" header="0" footer="0"/>

--- a/docs/Tableau_Synthese_E5.xlsx
+++ b/docs/Tableau_Synthese_E5.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\narmi\Desktop\portfolio1\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A19C42CF-B0EC-42E1-B4B7-124AB129E73E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2261FE3-086B-4A57-820E-3DE779965E01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="420" windowWidth="20025" windowHeight="13118" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="563" windowWidth="20025" windowHeight="13117" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
@@ -137,9 +137,6 @@
     <t>Réalisations en milieu professionnel en cours de première année</t>
   </si>
   <si>
-    <t>Validation et fiabilisation de rapports RH (SAP BO &amp; SQL)</t>
-  </si>
-  <si>
     <t>05-06/25</t>
   </si>
   <si>
@@ -177,6 +174,9 @@
   </si>
   <si>
     <t>GLPI Mise en œuvre d’un serveur LAMP  - Procédure d'installation (ProxMox)</t>
+  </si>
+  <si>
+    <t>Validation et fiabilisation de rapports et correction de requêtes RH (SAP BO &amp; SQL)</t>
   </si>
 </sst>
 </file>
@@ -1015,12 +1015,12 @@
         <v>7</v>
       </c>
       <c r="H4" s="20" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="29"/>
       <c r="C5" s="29"/>
@@ -1169,7 +1169,7 @@
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="12"/>
+      <c r="H10" s="10"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="12" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B12" s="21">
         <v>45962</v>
@@ -1231,9 +1231,9 @@
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
       <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
+      <c r="F12" s="12"/>
       <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
+      <c r="H12" s="10"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1260,7 +1260,7 @@
       <c r="B13" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="11"/>
       <c r="D13" s="11"/>
       <c r="E13" s="10"/>
       <c r="F13" s="11"/>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="14" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="21">
         <v>46113</v>
@@ -1295,7 +1295,7 @@
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="E14" s="12"/>
-      <c r="F14" s="10"/>
+      <c r="F14" s="12"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
       <c r="I14" s="1"/>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="15" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B15" s="9"/>
       <c r="C15" s="10"/>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="18" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C18" s="11"/>
       <c r="D18" s="11"/>
@@ -1439,10 +1439,10 @@
     </row>
     <row r="19" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="12"/>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="20" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="23"/>
       <c r="C20" s="23"/>
@@ -1529,10 +1529,10 @@
     </row>
     <row r="22" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C22" s="11"/>
       <c r="D22" s="10"/>
@@ -1561,15 +1561,15 @@
     </row>
     <row r="23" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="12"/>
       <c r="D23" s="12"/>
       <c r="E23" s="10"/>
-      <c r="F23" s="12"/>
+      <c r="F23" s="10"/>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
       <c r="I23" s="1"/>
@@ -1593,13 +1593,13 @@
     </row>
     <row r="24" spans="1:26" ht="39.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="10"/>
-      <c r="D24" s="11"/>
+      <c r="D24" s="10"/>
       <c r="E24" s="11"/>
       <c r="F24" s="10"/>
       <c r="G24" s="11"/>
